--- a/Data/g18.3.xlsx
+++ b/Data/g18.3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,13 +735,13 @@
         <v>2020</v>
       </c>
       <c r="B22" t="n">
-        <v>22.63548882549046</v>
+        <v>22.63893950014812</v>
       </c>
       <c r="C22" t="n">
-        <v>11.48481906767816</v>
+        <v>11.48384476288428</v>
       </c>
       <c r="D22" t="n">
-        <v>13.51093904698167</v>
+        <v>13.51292263323663</v>
       </c>
     </row>
     <row r="23">
@@ -749,13 +749,13 @@
         <v>2021</v>
       </c>
       <c r="B23" t="n">
-        <v>23.09893510493992</v>
+        <v>23.10205111542604</v>
       </c>
       <c r="C23" t="n">
-        <v>11.83471890624934</v>
+        <v>11.82207060912735</v>
       </c>
       <c r="D23" t="n">
-        <v>13.74061011986208</v>
+        <v>13.73975493952165</v>
       </c>
     </row>
     <row r="24">
@@ -763,13 +763,13 @@
         <v>2022</v>
       </c>
       <c r="B24" t="n">
-        <v>23.52577827880783</v>
+        <v>23.52576943454534</v>
       </c>
       <c r="C24" t="n">
-        <v>12.16101662962668</v>
+        <v>12.14280652156203</v>
       </c>
       <c r="D24" t="n">
-        <v>13.98682692633936</v>
+        <v>13.9850880466868</v>
       </c>
     </row>
     <row r="25">
@@ -777,13 +777,13 @@
         <v>2023</v>
       </c>
       <c r="B25" t="n">
-        <v>23.71146373109548</v>
+        <v>23.70296658052371</v>
       </c>
       <c r="C25" t="n">
-        <v>12.4483240726964</v>
+        <v>12.41664452075055</v>
       </c>
       <c r="D25" t="n">
-        <v>14.01600793116783</v>
+        <v>14.00565634327212</v>
       </c>
     </row>
     <row r="26">
@@ -791,13 +791,27 @@
         <v>2024</v>
       </c>
       <c r="B26" t="n">
-        <v>23.90207758604287</v>
+        <v>23.87442976981977</v>
       </c>
       <c r="C26" t="n">
-        <v>12.61414502123088</v>
+        <v>12.56732550153671</v>
       </c>
       <c r="D26" t="n">
-        <v>14.19608567023208</v>
+        <v>14.17958942302392</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B27" t="n">
+        <v>24.16057578250575</v>
+      </c>
+      <c r="C27" t="n">
+        <v>12.76037774955425</v>
+      </c>
+      <c r="D27" t="n">
+        <v>14.15576457281786</v>
       </c>
     </row>
   </sheetData>
